--- a/CAPM_Analysis.xlsx
+++ b/CAPM_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stevi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8786807F-2DC9-4318-A06C-ACCD708296A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202E2FE1-5DC3-42EF-8908-35EF241588FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="990" windowWidth="24375" windowHeight="12660" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-210" yWindow="0" windowWidth="27810" windowHeight="15585" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -384,9 +384,6 @@
     <t xml:space="preserve">P&amp;G has the highest beta. </t>
   </si>
   <si>
-    <t xml:space="preserve">P&amp;G had the highest beta and was the most sensitive to market movements among the companies analyzed. Beta ranged from 0.19 to 1.09, indicating differences in sensitivity to the overall market movements. </t>
-  </si>
-  <si>
     <t>U.S. Dept of Treasury- 13-Week Coupon</t>
   </si>
   <si>
@@ -400,6 +397,9 @@
   </si>
   <si>
     <t>Companies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P&amp;G had the highest beta and was the most sensitive to market movements among the companies analyzed. Beta ranged from 0.18 to 1.09, indicating differences in sensitivity to the overall market movements. </t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1084,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>CAPM Expected Return  vs Actual Annualized Return</a:t>
+              <a:t>CAPM Expected vs Actual Return</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1413,10 +1413,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.21152716719119288"/>
-          <c:y val="6.3926940639269403E-2"/>
-          <c:w val="0.57694566561761429"/>
-          <c:h val="5.1408424693182006E-2"/>
+          <c:x val="0.21152720448579185"/>
+          <c:y val="7.2090218456311209E-2"/>
+          <c:w val="0.57249401712420489"/>
+          <c:h val="5.2074624581214604E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -1749,11 +1749,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>371474</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>200024</xdr:rowOff>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6124575" cy="4467225"/>
+    <xdr:ext cx="6172199" cy="4410075"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
@@ -2119,7 +2119,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
@@ -2138,7 +2138,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,15 +2154,15 @@
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -6367,7 +6367,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
